--- a/02_DIA_inicio_2026_analisis_assets/rbd_9413_escuela-general-basica-santa-fe_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9413_escuela-general-basica-santa-fe_nt1_rubricas.xlsx
@@ -1980,13 +1980,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{599B36C9-E2AF-4202-97FD-4090E3BDF464}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7D3E6EB-0B26-4493-98AC-56A34F359D34}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6338CAC-88BB-4B90-883D-62D3018F6675}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7CC9E67-D024-4FD1-AA65-717ACA6B1E4B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6EEAB24-F470-4DF1-923B-FFA4E5BA6729}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECAF2A1E-E99F-4F87-B494-B5020E78CC0F}"/>
 </file>